--- a/data/master/metrocalm_vector_map_coordinate_workbook.xlsx
+++ b/data/master/metrocalm_vector_map_coordinate_workbook.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\home\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4417FCD-3867-484B-98C0-09F8C0DB5078}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96C98576-030E-4ABE-810B-D972E0C6E49F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9390" yWindow="3855" windowWidth="28800" windowHeight="15345" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="19410" windowHeight="20985" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Guide" sheetId="1" r:id="rId1"/>
@@ -16811,18 +16811,18 @@
         <v>627</v>
       </c>
       <c r="I95" s="7">
-        <v>3354</v>
+        <v>3584</v>
       </c>
       <c r="J95" s="7">
-        <v>1992</v>
+        <v>2140</v>
       </c>
       <c r="K95" s="11">
         <f>IF(I95="","",I95/Config!$B$2*100)</f>
-        <v>65.5078125</v>
+        <v>70</v>
       </c>
       <c r="L95" s="11">
         <f>IF(J95="","",J95/Config!$B$3*100)</f>
-        <v>69.166666666666671</v>
+        <v>74.305555555555557</v>
       </c>
       <c r="M95" s="5">
         <v>10</v>
@@ -16866,18 +16866,18 @@
         <v>627</v>
       </c>
       <c r="I96" s="7">
-        <v>3696</v>
+        <v>3862</v>
       </c>
       <c r="J96" s="7">
-        <v>1992</v>
+        <v>2140</v>
       </c>
       <c r="K96" s="11">
         <f>IF(I96="","",I96/Config!$B$2*100)</f>
-        <v>72.1875</v>
+        <v>75.4296875</v>
       </c>
       <c r="L96" s="11">
         <f>IF(J96="","",J96/Config!$B$3*100)</f>
-        <v>69.166666666666671</v>
+        <v>74.305555555555557</v>
       </c>
       <c r="M96" s="5">
         <v>12</v>
@@ -18746,18 +18746,18 @@
         <v>761</v>
       </c>
       <c r="I130" s="7">
-        <v>3696</v>
+        <v>3862</v>
       </c>
       <c r="J130" s="7">
-        <v>1992</v>
+        <v>2140</v>
       </c>
       <c r="K130" s="11">
         <f>IF(I130="","",I130/Config!$B$2*100)</f>
-        <v>72.1875</v>
+        <v>75.4296875</v>
       </c>
       <c r="L130" s="11">
         <f>IF(J130="","",J130/Config!$B$3*100)</f>
-        <v>69.166666666666671</v>
+        <v>74.305555555555557</v>
       </c>
       <c r="M130" s="5">
         <v>12</v>
@@ -20896,7 +20896,7 @@
         <v>4356</v>
       </c>
       <c r="J169" s="7">
-        <v>1868</v>
+        <v>1928</v>
       </c>
       <c r="K169" s="11">
         <f>IF(I169="","",I169/Config!$B$2*100)</f>
@@ -20904,7 +20904,7 @@
       </c>
       <c r="L169" s="11">
         <f>IF(J169="","",J169/Config!$B$3*100)</f>
-        <v>64.861111111111114</v>
+        <v>66.944444444444443</v>
       </c>
       <c r="M169" s="5">
         <v>10</v>
@@ -20951,7 +20951,7 @@
         <v>4356</v>
       </c>
       <c r="J170" s="7">
-        <v>1976</v>
+        <v>2096</v>
       </c>
       <c r="K170" s="11">
         <f>IF(I170="","",I170/Config!$B$2*100)</f>
@@ -20959,7 +20959,7 @@
       </c>
       <c r="L170" s="11">
         <f>IF(J170="","",J170/Config!$B$3*100)</f>
-        <v>68.611111111111114</v>
+        <v>72.777777777777771</v>
       </c>
       <c r="M170" s="5">
         <v>10</v>
@@ -21006,7 +21006,7 @@
         <v>4356</v>
       </c>
       <c r="J171" s="7">
-        <v>2084</v>
+        <v>2264</v>
       </c>
       <c r="K171" s="11">
         <f>IF(I171="","",I171/Config!$B$2*100)</f>
@@ -21014,7 +21014,7 @@
       </c>
       <c r="L171" s="11">
         <f>IF(J171="","",J171/Config!$B$3*100)</f>
-        <v>72.361111111111114</v>
+        <v>78.611111111111114</v>
       </c>
       <c r="M171" s="5">
         <v>10</v>
@@ -21063,7 +21063,7 @@
         <v>4356</v>
       </c>
       <c r="J172" s="7">
-        <v>2192</v>
+        <v>2436</v>
       </c>
       <c r="K172" s="11">
         <f>IF(I172="","",I172/Config!$B$2*100)</f>
@@ -21071,7 +21071,7 @@
       </c>
       <c r="L172" s="11">
         <f>IF(J172="","",J172/Config!$B$3*100)</f>
-        <v>76.111111111111114</v>
+        <v>84.583333333333329</v>
       </c>
       <c r="M172" s="5">
         <v>10</v>
@@ -21115,18 +21115,18 @@
         <v>761</v>
       </c>
       <c r="I173" s="7">
-        <v>3528</v>
+        <v>3574</v>
       </c>
       <c r="J173" s="7">
-        <v>1824</v>
+        <v>1862</v>
       </c>
       <c r="K173" s="11">
         <f>IF(I173="","",I173/Config!$B$2*100)</f>
-        <v>68.90625</v>
+        <v>69.8046875</v>
       </c>
       <c r="L173" s="11">
         <f>IF(J173="","",J173/Config!$B$3*100)</f>
-        <v>63.333333333333329</v>
+        <v>64.652777777777786</v>
       </c>
       <c r="M173" s="5">
         <v>10</v>
@@ -21170,18 +21170,18 @@
         <v>761</v>
       </c>
       <c r="I174" s="7">
-        <v>3584</v>
+        <v>3680</v>
       </c>
       <c r="J174" s="7">
-        <v>1882</v>
+        <v>1964</v>
       </c>
       <c r="K174" s="11">
         <f>IF(I174="","",I174/Config!$B$2*100)</f>
-        <v>70</v>
+        <v>71.875</v>
       </c>
       <c r="L174" s="11">
         <f>IF(J174="","",J174/Config!$B$3*100)</f>
-        <v>65.347222222222229</v>
+        <v>68.194444444444443</v>
       </c>
       <c r="M174" s="5">
         <v>10</v>
@@ -21225,18 +21225,18 @@
         <v>761</v>
       </c>
       <c r="I175" s="7">
-        <v>3640</v>
+        <v>3772</v>
       </c>
       <c r="J175" s="7">
-        <v>1936</v>
+        <v>2052</v>
       </c>
       <c r="K175" s="11">
         <f>IF(I175="","",I175/Config!$B$2*100)</f>
-        <v>71.09375</v>
+        <v>73.671875</v>
       </c>
       <c r="L175" s="11">
         <f>IF(J175="","",J175/Config!$B$3*100)</f>
-        <v>67.222222222222229</v>
+        <v>71.25</v>
       </c>
       <c r="M175" s="5">
         <v>10</v>
@@ -21280,18 +21280,18 @@
         <v>761</v>
       </c>
       <c r="I176" s="7">
-        <v>3760</v>
+        <v>3964</v>
       </c>
       <c r="J176" s="7">
-        <v>2056</v>
+        <v>2240</v>
       </c>
       <c r="K176" s="11">
         <f>IF(I176="","",I176/Config!$B$2*100)</f>
-        <v>73.4375</v>
+        <v>77.421875</v>
       </c>
       <c r="L176" s="11">
         <f>IF(J176="","",J176/Config!$B$3*100)</f>
-        <v>71.388888888888886</v>
+        <v>77.777777777777786</v>
       </c>
       <c r="M176" s="5">
         <v>10</v>
@@ -21335,18 +21335,18 @@
         <v>761</v>
       </c>
       <c r="I177" s="7">
-        <v>3824</v>
+        <v>4064</v>
       </c>
       <c r="J177" s="7">
-        <v>2120</v>
+        <v>2336</v>
       </c>
       <c r="K177" s="11">
         <f>IF(I177="","",I177/Config!$B$2*100)</f>
-        <v>74.6875</v>
+        <v>79.375</v>
       </c>
       <c r="L177" s="11">
         <f>IF(J177="","",J177/Config!$B$3*100)</f>
-        <v>73.611111111111114</v>
+        <v>81.111111111111114</v>
       </c>
       <c r="M177" s="5">
         <v>10</v>
@@ -21390,18 +21390,18 @@
         <v>761</v>
       </c>
       <c r="I178" s="7">
-        <v>3896</v>
+        <v>4164</v>
       </c>
       <c r="J178" s="7">
-        <v>2196</v>
+        <v>2436</v>
       </c>
       <c r="K178" s="11">
         <f>IF(I178="","",I178/Config!$B$2*100)</f>
-        <v>76.09375</v>
+        <v>81.328125</v>
       </c>
       <c r="L178" s="11">
         <f>IF(J178="","",J178/Config!$B$3*100)</f>
-        <v>76.25</v>
+        <v>84.583333333333329</v>
       </c>
       <c r="M178" s="5">
         <v>10</v>
@@ -22053,7 +22053,7 @@
         <v>1378</v>
       </c>
       <c r="J190" s="7">
-        <v>400</v>
+        <v>324</v>
       </c>
       <c r="K190" s="11">
         <f>IF(I190="","",I190/Config!$B$2*100)</f>
@@ -22061,7 +22061,7 @@
       </c>
       <c r="L190" s="11">
         <f>IF(J190="","",J190/Config!$B$3*100)</f>
-        <v>13.888888888888889</v>
+        <v>11.25</v>
       </c>
       <c r="M190" s="5">
         <v>10</v>
@@ -30906,19 +30906,19 @@
       </c>
       <c r="F90" s="8">
         <f>IFERROR(AVERAGEIF(Station_Visual_Nodes!$D:$D,B90,Station_Visual_Nodes!$I:$I),"")</f>
-        <v>3354</v>
+        <v>3584</v>
       </c>
       <c r="G90" s="8">
         <f>IFERROR(AVERAGEIF(Station_Visual_Nodes!$D:$D,B90,Station_Visual_Nodes!$J:$J),"")</f>
-        <v>1992</v>
+        <v>2140</v>
       </c>
       <c r="H90" s="11">
         <f>IF(F90="","",F90/Config!$B$2*100)</f>
-        <v>65.5078125</v>
+        <v>70</v>
       </c>
       <c r="I90" s="11">
         <f>IF(G90="","",G90/Config!$B$3*100)</f>
-        <v>69.166666666666671</v>
+        <v>74.305555555555557</v>
       </c>
       <c r="J90" s="5">
         <v>24</v>
@@ -30950,19 +30950,19 @@
       </c>
       <c r="F91" s="8">
         <f>IFERROR(AVERAGEIF(Station_Visual_Nodes!$D:$D,B91,Station_Visual_Nodes!$I:$I),"")</f>
-        <v>3696</v>
+        <v>3862</v>
       </c>
       <c r="G91" s="8">
         <f>IFERROR(AVERAGEIF(Station_Visual_Nodes!$D:$D,B91,Station_Visual_Nodes!$J:$J),"")</f>
-        <v>1992</v>
+        <v>2140</v>
       </c>
       <c r="H91" s="11">
         <f>IF(F91="","",F91/Config!$B$2*100)</f>
-        <v>72.1875</v>
+        <v>75.4296875</v>
       </c>
       <c r="I91" s="11">
         <f>IF(G91="","",G91/Config!$B$3*100)</f>
-        <v>69.166666666666671</v>
+        <v>74.305555555555557</v>
       </c>
       <c r="J91" s="5">
         <v>42</v>
@@ -33594,7 +33594,7 @@
       </c>
       <c r="G151" s="8">
         <f>IFERROR(AVERAGEIF(Station_Visual_Nodes!$D:$D,B151,Station_Visual_Nodes!$J:$J),"")</f>
-        <v>1868</v>
+        <v>1928</v>
       </c>
       <c r="H151" s="11">
         <f>IF(F151="","",F151/Config!$B$2*100)</f>
@@ -33602,7 +33602,7 @@
       </c>
       <c r="I151" s="11">
         <f>IF(G151="","",G151/Config!$B$3*100)</f>
-        <v>64.861111111111114</v>
+        <v>66.944444444444443</v>
       </c>
       <c r="J151" s="5">
         <v>24</v>
@@ -33638,7 +33638,7 @@
       </c>
       <c r="G152" s="8">
         <f>IFERROR(AVERAGEIF(Station_Visual_Nodes!$D:$D,B152,Station_Visual_Nodes!$J:$J),"")</f>
-        <v>1976</v>
+        <v>2096</v>
       </c>
       <c r="H152" s="11">
         <f>IF(F152="","",F152/Config!$B$2*100)</f>
@@ -33646,7 +33646,7 @@
       </c>
       <c r="I152" s="11">
         <f>IF(G152="","",G152/Config!$B$3*100)</f>
-        <v>68.611111111111114</v>
+        <v>72.777777777777771</v>
       </c>
       <c r="J152" s="5">
         <v>24</v>
@@ -33682,7 +33682,7 @@
       </c>
       <c r="G153" s="8">
         <f>IFERROR(AVERAGEIF(Station_Visual_Nodes!$D:$D,B153,Station_Visual_Nodes!$J:$J),"")</f>
-        <v>2084</v>
+        <v>2264</v>
       </c>
       <c r="H153" s="11">
         <f>IF(F153="","",F153/Config!$B$2*100)</f>
@@ -33690,7 +33690,7 @@
       </c>
       <c r="I153" s="11">
         <f>IF(G153="","",G153/Config!$B$3*100)</f>
-        <v>72.361111111111114</v>
+        <v>78.611111111111114</v>
       </c>
       <c r="J153" s="5">
         <v>24</v>
@@ -33726,7 +33726,7 @@
       </c>
       <c r="G154" s="8">
         <f>IFERROR(AVERAGEIF(Station_Visual_Nodes!$D:$D,B154,Station_Visual_Nodes!$J:$J),"")</f>
-        <v>2192</v>
+        <v>2436</v>
       </c>
       <c r="H154" s="11">
         <f>IF(F154="","",F154/Config!$B$2*100)</f>
@@ -33734,7 +33734,7 @@
       </c>
       <c r="I154" s="11">
         <f>IF(G154="","",G154/Config!$B$3*100)</f>
-        <v>76.111111111111114</v>
+        <v>84.583333333333329</v>
       </c>
       <c r="J154" s="5">
         <v>24</v>
@@ -33766,19 +33766,19 @@
       </c>
       <c r="F155" s="8">
         <f>IFERROR(AVERAGEIF(Station_Visual_Nodes!$D:$D,B155,Station_Visual_Nodes!$I:$I),"")</f>
-        <v>3528</v>
+        <v>3574</v>
       </c>
       <c r="G155" s="8">
         <f>IFERROR(AVERAGEIF(Station_Visual_Nodes!$D:$D,B155,Station_Visual_Nodes!$J:$J),"")</f>
-        <v>1824</v>
+        <v>1862</v>
       </c>
       <c r="H155" s="11">
         <f>IF(F155="","",F155/Config!$B$2*100)</f>
-        <v>68.90625</v>
+        <v>69.8046875</v>
       </c>
       <c r="I155" s="11">
         <f>IF(G155="","",G155/Config!$B$3*100)</f>
-        <v>63.333333333333329</v>
+        <v>64.652777777777786</v>
       </c>
       <c r="J155" s="5">
         <v>24</v>
@@ -33810,19 +33810,19 @@
       </c>
       <c r="F156" s="8">
         <f>IFERROR(AVERAGEIF(Station_Visual_Nodes!$D:$D,B156,Station_Visual_Nodes!$I:$I),"")</f>
-        <v>3584</v>
+        <v>3680</v>
       </c>
       <c r="G156" s="8">
         <f>IFERROR(AVERAGEIF(Station_Visual_Nodes!$D:$D,B156,Station_Visual_Nodes!$J:$J),"")</f>
-        <v>1882</v>
+        <v>1964</v>
       </c>
       <c r="H156" s="11">
         <f>IF(F156="","",F156/Config!$B$2*100)</f>
-        <v>70</v>
+        <v>71.875</v>
       </c>
       <c r="I156" s="11">
         <f>IF(G156="","",G156/Config!$B$3*100)</f>
-        <v>65.347222222222229</v>
+        <v>68.194444444444443</v>
       </c>
       <c r="J156" s="5">
         <v>24</v>
@@ -33854,19 +33854,19 @@
       </c>
       <c r="F157" s="8">
         <f>IFERROR(AVERAGEIF(Station_Visual_Nodes!$D:$D,B157,Station_Visual_Nodes!$I:$I),"")</f>
-        <v>3640</v>
+        <v>3772</v>
       </c>
       <c r="G157" s="8">
         <f>IFERROR(AVERAGEIF(Station_Visual_Nodes!$D:$D,B157,Station_Visual_Nodes!$J:$J),"")</f>
-        <v>1936</v>
+        <v>2052</v>
       </c>
       <c r="H157" s="11">
         <f>IF(F157="","",F157/Config!$B$2*100)</f>
-        <v>71.09375</v>
+        <v>73.671875</v>
       </c>
       <c r="I157" s="11">
         <f>IF(G157="","",G157/Config!$B$3*100)</f>
-        <v>67.222222222222229</v>
+        <v>71.25</v>
       </c>
       <c r="J157" s="5">
         <v>24</v>
@@ -33898,19 +33898,19 @@
       </c>
       <c r="F158" s="8">
         <f>IFERROR(AVERAGEIF(Station_Visual_Nodes!$D:$D,B158,Station_Visual_Nodes!$I:$I),"")</f>
-        <v>3760</v>
+        <v>3964</v>
       </c>
       <c r="G158" s="8">
         <f>IFERROR(AVERAGEIF(Station_Visual_Nodes!$D:$D,B158,Station_Visual_Nodes!$J:$J),"")</f>
-        <v>2056</v>
+        <v>2240</v>
       </c>
       <c r="H158" s="11">
         <f>IF(F158="","",F158/Config!$B$2*100)</f>
-        <v>73.4375</v>
+        <v>77.421875</v>
       </c>
       <c r="I158" s="11">
         <f>IF(G158="","",G158/Config!$B$3*100)</f>
-        <v>71.388888888888886</v>
+        <v>77.777777777777786</v>
       </c>
       <c r="J158" s="5">
         <v>24</v>
@@ -33942,19 +33942,19 @@
       </c>
       <c r="F159" s="8">
         <f>IFERROR(AVERAGEIF(Station_Visual_Nodes!$D:$D,B159,Station_Visual_Nodes!$I:$I),"")</f>
-        <v>3824</v>
+        <v>4064</v>
       </c>
       <c r="G159" s="8">
         <f>IFERROR(AVERAGEIF(Station_Visual_Nodes!$D:$D,B159,Station_Visual_Nodes!$J:$J),"")</f>
-        <v>2120</v>
+        <v>2336</v>
       </c>
       <c r="H159" s="11">
         <f>IF(F159="","",F159/Config!$B$2*100)</f>
-        <v>74.6875</v>
+        <v>79.375</v>
       </c>
       <c r="I159" s="11">
         <f>IF(G159="","",G159/Config!$B$3*100)</f>
-        <v>73.611111111111114</v>
+        <v>81.111111111111114</v>
       </c>
       <c r="J159" s="5">
         <v>24</v>
@@ -33986,19 +33986,19 @@
       </c>
       <c r="F160" s="8">
         <f>IFERROR(AVERAGEIF(Station_Visual_Nodes!$D:$D,B160,Station_Visual_Nodes!$I:$I),"")</f>
-        <v>3896</v>
+        <v>4164</v>
       </c>
       <c r="G160" s="8">
         <f>IFERROR(AVERAGEIF(Station_Visual_Nodes!$D:$D,B160,Station_Visual_Nodes!$J:$J),"")</f>
-        <v>2196</v>
+        <v>2436</v>
       </c>
       <c r="H160" s="11">
         <f>IF(F160="","",F160/Config!$B$2*100)</f>
-        <v>76.09375</v>
+        <v>81.328125</v>
       </c>
       <c r="I160" s="11">
         <f>IF(G160="","",G160/Config!$B$3*100)</f>
-        <v>76.25</v>
+        <v>84.583333333333329</v>
       </c>
       <c r="J160" s="5">
         <v>24</v>
@@ -34122,7 +34122,7 @@
       </c>
       <c r="G163" s="8">
         <f>IFERROR(AVERAGEIF(Station_Visual_Nodes!$D:$D,B163,Station_Visual_Nodes!$J:$J),"")</f>
-        <v>400</v>
+        <v>324</v>
       </c>
       <c r="H163" s="11">
         <f>IF(F163="","",F163/Config!$B$2*100)</f>
@@ -34130,7 +34130,7 @@
       </c>
       <c r="I163" s="11">
         <f>IF(G163="","",G163/Config!$B$3*100)</f>
-        <v>13.888888888888889</v>
+        <v>11.25</v>
       </c>
       <c r="J163" s="5">
         <v>24</v>
@@ -42091,19 +42091,19 @@
       </c>
       <c r="F90" s="9">
         <f>IFERROR(INDEX(Station_Click_Areas!$F:$F,MATCH(B90,Station_Click_Areas!$B:$B,0)),"")</f>
-        <v>3354</v>
+        <v>3584</v>
       </c>
       <c r="G90" s="9">
         <f>IFERROR(INDEX(Station_Click_Areas!$G:$G,MATCH(B90,Station_Click_Areas!$B:$B,0)),"")</f>
-        <v>1992</v>
+        <v>2140</v>
       </c>
       <c r="H90" s="11">
         <f>IF(F90="","",F90/Config!$B$2*100)</f>
-        <v>65.5078125</v>
+        <v>70</v>
       </c>
       <c r="I90" s="11">
         <f>IF(G90="","",G90/Config!$B$3*100)</f>
-        <v>69.166666666666671</v>
+        <v>74.305555555555557</v>
       </c>
       <c r="J90" s="5">
         <v>10.5</v>
@@ -42141,19 +42141,19 @@
       </c>
       <c r="F91" s="9">
         <f>IFERROR(INDEX(Station_Click_Areas!$F:$F,MATCH(B91,Station_Click_Areas!$B:$B,0)),"")</f>
-        <v>3696</v>
+        <v>3862</v>
       </c>
       <c r="G91" s="9">
         <f>IFERROR(INDEX(Station_Click_Areas!$G:$G,MATCH(B91,Station_Click_Areas!$B:$B,0)),"")</f>
-        <v>1992</v>
+        <v>2140</v>
       </c>
       <c r="H91" s="11">
         <f>IF(F91="","",F91/Config!$B$2*100)</f>
-        <v>72.1875</v>
+        <v>75.4296875</v>
       </c>
       <c r="I91" s="11">
         <f>IF(G91="","",G91/Config!$B$3*100)</f>
-        <v>69.166666666666671</v>
+        <v>74.305555555555557</v>
       </c>
       <c r="J91" s="5">
         <v>12</v>
@@ -45145,7 +45145,7 @@
       </c>
       <c r="G151" s="9">
         <f>IFERROR(INDEX(Station_Click_Areas!$G:$G,MATCH(B151,Station_Click_Areas!$B:$B,0)),"")</f>
-        <v>1868</v>
+        <v>1928</v>
       </c>
       <c r="H151" s="11">
         <f>IF(F151="","",F151/Config!$B$2*100)</f>
@@ -45153,7 +45153,7 @@
       </c>
       <c r="I151" s="11">
         <f>IF(G151="","",G151/Config!$B$3*100)</f>
-        <v>64.861111111111114</v>
+        <v>66.944444444444443</v>
       </c>
       <c r="J151" s="5">
         <v>10.5</v>
@@ -45195,7 +45195,7 @@
       </c>
       <c r="G152" s="9">
         <f>IFERROR(INDEX(Station_Click_Areas!$G:$G,MATCH(B152,Station_Click_Areas!$B:$B,0)),"")</f>
-        <v>1976</v>
+        <v>2096</v>
       </c>
       <c r="H152" s="11">
         <f>IF(F152="","",F152/Config!$B$2*100)</f>
@@ -45203,7 +45203,7 @@
       </c>
       <c r="I152" s="11">
         <f>IF(G152="","",G152/Config!$B$3*100)</f>
-        <v>68.611111111111114</v>
+        <v>72.777777777777771</v>
       </c>
       <c r="J152" s="5">
         <v>10.5</v>
@@ -45245,7 +45245,7 @@
       </c>
       <c r="G153" s="9">
         <f>IFERROR(INDEX(Station_Click_Areas!$G:$G,MATCH(B153,Station_Click_Areas!$B:$B,0)),"")</f>
-        <v>2084</v>
+        <v>2264</v>
       </c>
       <c r="H153" s="11">
         <f>IF(F153="","",F153/Config!$B$2*100)</f>
@@ -45253,7 +45253,7 @@
       </c>
       <c r="I153" s="11">
         <f>IF(G153="","",G153/Config!$B$3*100)</f>
-        <v>72.361111111111114</v>
+        <v>78.611111111111114</v>
       </c>
       <c r="J153" s="5">
         <v>10.5</v>
@@ -45295,7 +45295,7 @@
       </c>
       <c r="G154" s="9">
         <f>IFERROR(INDEX(Station_Click_Areas!$G:$G,MATCH(B154,Station_Click_Areas!$B:$B,0)),"")</f>
-        <v>2192</v>
+        <v>2436</v>
       </c>
       <c r="H154" s="11">
         <f>IF(F154="","",F154/Config!$B$2*100)</f>
@@ -45303,7 +45303,7 @@
       </c>
       <c r="I154" s="11">
         <f>IF(G154="","",G154/Config!$B$3*100)</f>
-        <v>76.111111111111114</v>
+        <v>84.583333333333329</v>
       </c>
       <c r="J154" s="5">
         <v>10.5</v>
@@ -45341,19 +45341,19 @@
       </c>
       <c r="F155" s="9">
         <f>IFERROR(INDEX(Station_Click_Areas!$F:$F,MATCH(B155,Station_Click_Areas!$B:$B,0)),"")</f>
-        <v>3528</v>
+        <v>3574</v>
       </c>
       <c r="G155" s="9">
         <f>IFERROR(INDEX(Station_Click_Areas!$G:$G,MATCH(B155,Station_Click_Areas!$B:$B,0)),"")</f>
-        <v>1824</v>
+        <v>1862</v>
       </c>
       <c r="H155" s="11">
         <f>IF(F155="","",F155/Config!$B$2*100)</f>
-        <v>68.90625</v>
+        <v>69.8046875</v>
       </c>
       <c r="I155" s="11">
         <f>IF(G155="","",G155/Config!$B$3*100)</f>
-        <v>63.333333333333329</v>
+        <v>64.652777777777786</v>
       </c>
       <c r="J155" s="5">
         <v>10.5</v>
@@ -45391,19 +45391,19 @@
       </c>
       <c r="F156" s="9">
         <f>IFERROR(INDEX(Station_Click_Areas!$F:$F,MATCH(B156,Station_Click_Areas!$B:$B,0)),"")</f>
-        <v>3584</v>
+        <v>3680</v>
       </c>
       <c r="G156" s="9">
         <f>IFERROR(INDEX(Station_Click_Areas!$G:$G,MATCH(B156,Station_Click_Areas!$B:$B,0)),"")</f>
-        <v>1882</v>
+        <v>1964</v>
       </c>
       <c r="H156" s="11">
         <f>IF(F156="","",F156/Config!$B$2*100)</f>
-        <v>70</v>
+        <v>71.875</v>
       </c>
       <c r="I156" s="11">
         <f>IF(G156="","",G156/Config!$B$3*100)</f>
-        <v>65.347222222222229</v>
+        <v>68.194444444444443</v>
       </c>
       <c r="J156" s="5">
         <v>10.5</v>
@@ -45441,19 +45441,19 @@
       </c>
       <c r="F157" s="9">
         <f>IFERROR(INDEX(Station_Click_Areas!$F:$F,MATCH(B157,Station_Click_Areas!$B:$B,0)),"")</f>
-        <v>3640</v>
+        <v>3772</v>
       </c>
       <c r="G157" s="9">
         <f>IFERROR(INDEX(Station_Click_Areas!$G:$G,MATCH(B157,Station_Click_Areas!$B:$B,0)),"")</f>
-        <v>1936</v>
+        <v>2052</v>
       </c>
       <c r="H157" s="11">
         <f>IF(F157="","",F157/Config!$B$2*100)</f>
-        <v>71.09375</v>
+        <v>73.671875</v>
       </c>
       <c r="I157" s="11">
         <f>IF(G157="","",G157/Config!$B$3*100)</f>
-        <v>67.222222222222229</v>
+        <v>71.25</v>
       </c>
       <c r="J157" s="5">
         <v>10.5</v>
@@ -45491,19 +45491,19 @@
       </c>
       <c r="F158" s="9">
         <f>IFERROR(INDEX(Station_Click_Areas!$F:$F,MATCH(B158,Station_Click_Areas!$B:$B,0)),"")</f>
-        <v>3760</v>
+        <v>3964</v>
       </c>
       <c r="G158" s="9">
         <f>IFERROR(INDEX(Station_Click_Areas!$G:$G,MATCH(B158,Station_Click_Areas!$B:$B,0)),"")</f>
-        <v>2056</v>
+        <v>2240</v>
       </c>
       <c r="H158" s="11">
         <f>IF(F158="","",F158/Config!$B$2*100)</f>
-        <v>73.4375</v>
+        <v>77.421875</v>
       </c>
       <c r="I158" s="11">
         <f>IF(G158="","",G158/Config!$B$3*100)</f>
-        <v>71.388888888888886</v>
+        <v>77.777777777777786</v>
       </c>
       <c r="J158" s="5">
         <v>10.5</v>
@@ -45541,19 +45541,19 @@
       </c>
       <c r="F159" s="9">
         <f>IFERROR(INDEX(Station_Click_Areas!$F:$F,MATCH(B159,Station_Click_Areas!$B:$B,0)),"")</f>
-        <v>3824</v>
+        <v>4064</v>
       </c>
       <c r="G159" s="9">
         <f>IFERROR(INDEX(Station_Click_Areas!$G:$G,MATCH(B159,Station_Click_Areas!$B:$B,0)),"")</f>
-        <v>2120</v>
+        <v>2336</v>
       </c>
       <c r="H159" s="11">
         <f>IF(F159="","",F159/Config!$B$2*100)</f>
-        <v>74.6875</v>
+        <v>79.375</v>
       </c>
       <c r="I159" s="11">
         <f>IF(G159="","",G159/Config!$B$3*100)</f>
-        <v>73.611111111111114</v>
+        <v>81.111111111111114</v>
       </c>
       <c r="J159" s="5">
         <v>10.5</v>
@@ -45591,19 +45591,19 @@
       </c>
       <c r="F160" s="9">
         <f>IFERROR(INDEX(Station_Click_Areas!$F:$F,MATCH(B160,Station_Click_Areas!$B:$B,0)),"")</f>
-        <v>3896</v>
+        <v>4164</v>
       </c>
       <c r="G160" s="9">
         <f>IFERROR(INDEX(Station_Click_Areas!$G:$G,MATCH(B160,Station_Click_Areas!$B:$B,0)),"")</f>
-        <v>2196</v>
+        <v>2436</v>
       </c>
       <c r="H160" s="11">
         <f>IF(F160="","",F160/Config!$B$2*100)</f>
-        <v>76.09375</v>
+        <v>81.328125</v>
       </c>
       <c r="I160" s="11">
         <f>IF(G160="","",G160/Config!$B$3*100)</f>
-        <v>76.25</v>
+        <v>84.583333333333329</v>
       </c>
       <c r="J160" s="5">
         <v>10.5</v>
@@ -45745,7 +45745,7 @@
       </c>
       <c r="G163" s="9">
         <f>IFERROR(INDEX(Station_Click_Areas!$G:$G,MATCH(B163,Station_Click_Areas!$B:$B,0)),"")</f>
-        <v>400</v>
+        <v>324</v>
       </c>
       <c r="H163" s="11">
         <f>IF(F163="","",F163/Config!$B$2*100)</f>
@@ -45753,7 +45753,7 @@
       </c>
       <c r="I163" s="11">
         <f>IF(G163="","",G163/Config!$B$3*100)</f>
-        <v>13.888888888888889</v>
+        <v>11.25</v>
       </c>
       <c r="J163" s="5">
         <v>10.5</v>

--- a/data/master/metrocalm_vector_map_coordinate_workbook.xlsx
+++ b/data/master/metrocalm_vector_map_coordinate_workbook.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\home\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96C98576-030E-4ABE-810B-D972E0C6E49F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BCDF939-0C9C-4E92-A031-C4C64FF75DF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-105" yWindow="0" windowWidth="19410" windowHeight="20985" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18195,7 +18195,7 @@
         <v>2200</v>
       </c>
       <c r="J120" s="7">
-        <v>1788</v>
+        <v>1750</v>
       </c>
       <c r="K120" s="11">
         <f>IF(I120="","",I120/Config!$B$2*100)</f>
@@ -18203,7 +18203,7 @@
       </c>
       <c r="L120" s="11">
         <f>IF(J120="","",J120/Config!$B$3*100)</f>
-        <v>62.083333333333336</v>
+        <v>60.763888888888886</v>
       </c>
       <c r="M120" s="5">
         <v>10</v>
@@ -31790,7 +31790,7 @@
       </c>
       <c r="G110" s="8">
         <f>IFERROR(AVERAGEIF(Station_Visual_Nodes!$D:$D,B110,Station_Visual_Nodes!$J:$J),"")</f>
-        <v>1788</v>
+        <v>1750</v>
       </c>
       <c r="H110" s="11">
         <f>IF(F110="","",F110/Config!$B$2*100)</f>
@@ -31798,7 +31798,7 @@
       </c>
       <c r="I110" s="11">
         <f>IF(G110="","",G110/Config!$B$3*100)</f>
-        <v>62.083333333333336</v>
+        <v>60.763888888888886</v>
       </c>
       <c r="J110" s="5">
         <v>24</v>
@@ -43095,7 +43095,7 @@
       </c>
       <c r="G110" s="9">
         <f>IFERROR(INDEX(Station_Click_Areas!$G:$G,MATCH(B110,Station_Click_Areas!$B:$B,0)),"")</f>
-        <v>1788</v>
+        <v>1750</v>
       </c>
       <c r="H110" s="11">
         <f>IF(F110="","",F110/Config!$B$2*100)</f>
@@ -43103,7 +43103,7 @@
       </c>
       <c r="I110" s="11">
         <f>IF(G110="","",G110/Config!$B$3*100)</f>
-        <v>62.083333333333336</v>
+        <v>60.763888888888886</v>
       </c>
       <c r="J110" s="5">
         <v>10.5</v>
